--- a/Assessment Questions/CDE/Big Data Advance/KAFKA and Spark/Kafka architecture/Kafka_Architecture.xlsx
+++ b/Assessment Questions/CDE/Big Data Advance/KAFKA and Spark/Kafka architecture/Kafka_Architecture.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kafka Architecture" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +439,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -466,7 +466,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>A) Store and serve messages</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -486,10 +486,9 @@
           <t>What is the fundamental unit of data storage in Kafka?</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Partition</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -516,7 +515,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>B) Zookeeper/KRaft</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -536,10 +535,9 @@
           <t>A company has 3 brokers and a topic with replication factor 3. If one broker goes down, can consumers still read from that topic? Why?</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yes, because the remaining 2 replicas still contain the data</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -559,10 +557,9 @@
           <t>What is the term for a Kafka cluster without Zookeeper using Raft protocol?</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KRaft</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -589,7 +586,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>B) 9092</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -616,7 +613,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>A) In-Sync Replicas</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -636,10 +633,9 @@
           <t>Which component tracks consumer offsets in Kafka?</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Consumer Group</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -659,10 +655,9 @@
           <t>A producer sends messages to a topic with 6 partitions. The producer uses a custom partitioner based on user_id. What determines which partition the message goes to?</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The hash of user_id modulo number of partitions</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -689,7 +684,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>B) Cluster metadata management</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -709,10 +704,9 @@
           <t>What is the leader replica responsible for?</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>All read/write operations</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -739,7 +733,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>C) ElasticSearch</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -759,10 +753,9 @@
           <t>A topic has 8 partitions and a consumer group with 5 consumers. How many consumers will be idle?</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3 consumers idle (5 consumers, 8 partitions = 3 idle, 5 active)</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -782,10 +775,9 @@
           <t>What is the term for the immutable sequence of records in a partition?</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Log</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -812,7 +804,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>C) 1 GB</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -839,7 +831,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>C) Unique ID within partition</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -859,10 +851,9 @@
           <t>A company needs exactly-once processing. Which Kafka feature enables this?</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Idempotent producer and transactional API</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -882,10 +873,9 @@
           <t>What is the storage location for Kafka data on disk?</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>/tmp/kafka-logs or configured log.dirs</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -912,7 +902,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>B) Consumer API</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -932,10 +922,9 @@
           <t>What is the controller in Kafka architecture responsible for?</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Managing partition leaders and cluster metadata</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
